--- a/results/exp05-c100-resnet-bw1-50-fedavg-old-drop25/20260924-070058/rounds.xlsx
+++ b/results/exp05-c100-resnet-bw1-50-fedavg-old-drop25/20260924-070058/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2942,6 +2942,5899 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:29:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.097636219740425</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="G31" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="H31" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" t="n">
+        <v>55.5338</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0:55.53</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>54.1315</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.2691</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1681.8784</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>28:01.88</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:35;1:20;9:31;4:29;0:10;8:23;6:6;7:7;3:33;2:15</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[0,4,6];1:[3];9:[4,6];4:[4];0:[4];8:[4,6];6:[];7:[];3:[2,5,7];2:[5]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=35,experts=[0,4,6]; c1:bw=20,experts=[3]; c9:bw=31,experts=[4,6]; c4:bw=29,experts=[4]; c0:bw=10,experts=[4]; c8:bw=23,experts=[4,6]; c6:bw=6,experts=[]; c7:bw=7,experts=[]; c3:bw=33,experts=[2,5,7]; c2:bw=15,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>6.6457,4.5955,3.7569,7.2170,5.0205,5.5926,7.0116,4.8427,5.3360,4.1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:29:56</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.07007305007719</v>
+      </c>
+      <c r="F32" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="G32" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="H32" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" t="n">
+        <v>55.643</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0:55.64</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>54.2126</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.2911</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1737.5407</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>28:57.54</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:17;4:11;9:25;1:17;5:35;8:19;3:13;2:9;0:27;7:36</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[0];4:[];9:[4];1:[5];5:[1,4];8:[0];3:[4];2:[];0:[4,6];7:[2,5,7]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[0]; c4:bw=11,experts=[]; c9:bw=25,experts=[4]; c1:bw=17,experts=[5]; c5:bw=35,experts=[1,4]; c8:bw=19,experts=[0]; c3:bw=13,experts=[4]; c2:bw=9,experts=[]; c0:bw=27,experts=[4,6]; c7:bw=36,experts=[2,5,7]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>7.0572,7.2048,3.7577,4.5307,6.7920,5.6642,5.4141,3.9309,4.9736,4.8872</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:30:51</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.048607840016289</v>
+      </c>
+      <c r="F33" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="G33" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="H33" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" t="n">
+        <v>55.5843</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0:55.58</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>54.1759</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.2629</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1793.1442</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>29:53.14</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:12;5:20;4:28;7:27;0:26;1:12;3:16;6:15;2:30;9:18</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[1];5:[4,6];4:[0];7:[4,6];0:[1,4];1:[7];3:[6];6:[1];2:[0,6,7];9:[0]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[1]; c5:bw=20,experts=[4,6]; c4:bw=28,experts=[0]; c7:bw=27,experts=[4,6]; c0:bw=26,experts=[1,4]; c1:bw=12,experts=[7]; c3:bw=16,experts=[6]; c6:bw=15,experts=[1]; c2:bw=30,experts=[0,6,7]; c9:bw=18,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>5.7832,6.6880,7.1529,4.8245,4.9634,4.6993,5.3692,6.9478,4.0568,3.6908</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:31:47</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.975037752927441</v>
+      </c>
+      <c r="F34" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="G34" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>55.5377</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0:55.54</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>54.2482</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.1505</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1848.9102</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>30:48.91</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:30;1:19;3:40;6:21;5:17;9:24;2:13;8:28;4:26;0:35</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[0,4];1:[0];3:[0,4,6];6:[4,6];5:[3];9:[1,4];2:[];8:[3,4];4:[1,6];0:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=30,experts=[0,4]; c1:bw=19,experts=[0]; c3:bw=40,experts=[0,4,6]; c6:bw=21,experts=[4,6]; c5:bw=17,experts=[3]; c9:bw=24,experts=[1,4]; c2:bw=13,experts=[]; c8:bw=28,experts=[3,4]; c4:bw=26,experts=[1,6]; c0:bw=35,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>4.8728,4.7492,5.5318,7.1491,6.5779,3.6938,4.1295,5.6293,7.3147,4.5998</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:32:42</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.92589340141835</v>
+      </c>
+      <c r="F35" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="G35" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>55.2956</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0:55.30</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>53.9985</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.1572</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1904.2252</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>31:44.23</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:26;1:26;6:27;9:38;8:24;0:13;5:34;7:18;3:41;2:30</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[3,5];1:[4,6];6:[3];9:[3,4,5];8:[4,6];0:[];5:[2,4];7:[1];3:[0,1,4,6];2:[1,2,4]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=26,experts=[3,5]; c1:bw=26,experts=[4,6]; c6:bw=27,experts=[3]; c9:bw=38,experts=[3,4,5]; c8:bw=24,experts=[4,6]; c0:bw=13,experts=[]; c5:bw=34,experts=[2,4]; c7:bw=18,experts=[1]; c3:bw=41,experts=[0,1,4,6]; c2:bw=30,experts=[1,2,4]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7.4418,4.8544,7.3166,3.8163,5.8638,5.1516,6.1162,4.6965,5.0266,3.7148</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:33:38</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.984261590283185</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="H36" t="n">
+        <v>34</v>
+      </c>
+      <c r="I36" t="n">
+        <v>55.4749</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0:55.47</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>54.0528</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.2846</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1959.7233</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>32:39.72</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:19;0:11;1:17;6:25;2:26;8:28;9:15;7:27;5:23;3:14</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[7];0:[2];1:[1];6:[2,5];2:[4,6];8:[2,7];9:[7];7:[3];5:[4,7];3:[]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=19,experts=[7]; c0:bw=11,experts=[2]; c1:bw=17,experts=[1]; c6:bw=25,experts=[2,5]; c2:bw=26,experts=[4,6]; c8:bw=28,experts=[2,7]; c9:bw=15,experts=[7]; c7:bw=27,experts=[3]; c5:bw=23,experts=[4,7]; c3:bw=14,experts=[]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>6.8584,5.1365,4.7202,7.0816,3.9640,5.6553,3.7032,4.8720,6.6944,5.3672</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:34:34</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.931734217545976</v>
+      </c>
+      <c r="F37" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="G37" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>55.8546</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0:55.85</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>54.4422</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.2416</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2015.598</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>33:35.60</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:21;0:20;3:34;7:15;6:24;5:28;1:5;4:42;8:29;2:29</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[4,6];0:[3,5];3:[3,4,6];7:[4];6:[4,7];5:[4,6];1:[];4:[0,4,5,6];8:[5];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=21,experts=[4,6]; c0:bw=20,experts=[3,5]; c3:bw=34,experts=[3,4,6]; c7:bw=15,experts=[4]; c6:bw=24,experts=[4,7]; c5:bw=28,experts=[4,6]; c1:bw=5,experts=[]; c4:bw=42,experts=[0,4,5,6]; c8:bw=29,experts=[5]; c2:bw=29,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>3.7284,4.9778,5.4313,4.8635,7.1732,6.5668,4.5722,7.2162,5.8771,4.0358</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:35:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.878601476567651</v>
+      </c>
+      <c r="F38" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="G38" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>56.1317</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0:56.13</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>54.7166</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.2618</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2071.7518</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>34:31.75</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:10;5:22;2:20;6:37;4:22;7:24;9:23;0:31;3:20;8:3</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[2];5:[4,5];2:[3,4];6:[4,6];4:[2,4];7:[4,6];9:[2,4];0:[4,7];3:[4,6];8:[]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[2]; c5:bw=22,experts=[4,5]; c2:bw=20,experts=[3,4]; c6:bw=37,experts=[4,6]; c4:bw=22,experts=[2,4]; c7:bw=24,experts=[4,6]; c9:bw=23,experts=[2,4]; c0:bw=31,experts=[4,7]; c3:bw=20,experts=[4,6]; c8:bw=3,experts=[]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>4.6338,6.7603,3.9777,7.0882,7.3425,4.8988,3.7673,4.9392,5.4203,5.8885</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:36:26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.863549604333697</v>
+      </c>
+      <c r="F39" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="G39" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37</v>
+      </c>
+      <c r="I39" t="n">
+        <v>55.7088</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0:55.71</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>54.3199</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.2528</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2127.4861</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>35:27.49</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:26;6:10;4:29;1:18;5:1;2:2;3:22;7:29;9:15;0:23</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[4];4:[4,6];1:[3];5:[];2:[];3:[2,5];7:[4,6];9:[4];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=26,experts=[4,6]; c6:bw=10,experts=[4]; c4:bw=29,experts=[4,6]; c1:bw=18,experts=[3]; c5:bw=1,experts=[]; c2:bw=2,experts=[]; c3:bw=22,experts=[2,5]; c7:bw=29,experts=[4,6]; c9:bw=15,experts=[4]; c0:bw=23,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>5.7576,7.0425,7.1273,4.5981,6.7592,3.9651,5.4947,4.8600,3.6986,5.0168</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:37:21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.878785803134768</v>
+      </c>
+      <c r="F40" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="G40" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="H40" t="n">
+        <v>37</v>
+      </c>
+      <c r="I40" t="n">
+        <v>55.5282</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0:55.53</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>54.1307</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1497</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.2466</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2183.0348</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>36:23.03</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:15;0:2;1:25;7:23;6:17;8:25;2:20;4:20;9:13;5:42</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[7];0:[];1:[4,5];7:[2];6:[];8:[0,4];2:[5];4:[4,6];9:[4];5:[0,1,4,6]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=15,experts=[7]; c0:bw=2,experts=[]; c1:bw=25,experts=[4,5]; c7:bw=23,experts=[2]; c6:bw=17,experts=[]; c8:bw=25,experts=[0,4]; c2:bw=20,experts=[5]; c4:bw=20,experts=[4,6]; c9:bw=13,experts=[4]; c5:bw=42,experts=[0,1,4,6]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5.6163,4.9659,4.5658,4.8185,7.0205,5.7342,3.9746,7.1020,3.7284,6.6045</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:38:17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.84168263273693</v>
+      </c>
+      <c r="F41" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="G41" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="H41" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" t="n">
+        <v>56.2147</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0:56.21</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>54.8107</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.2658</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2239.2758</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>37:19.28</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:15;1:24;5:18;6:26;2:37;7:38;3:4;4:11;9:22;0:20</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[1];1:[7];5:[4];6:[0,1];2:[0,4,7];7:[4,5,7];3:[];4:[];9:[0,4];0:[1,4]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=15,experts=[1]; c1:bw=24,experts=[7]; c5:bw=18,experts=[4]; c6:bw=26,experts=[0,1]; c2:bw=37,experts=[0,4,7]; c7:bw=38,experts=[4,5,7]; c3:bw=4,experts=[]; c4:bw=11,experts=[]; c9:bw=22,experts=[0,4]; c0:bw=20,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>5.8727,4.7870,6.8954,7.1243,3.9931,4.8763,5.4932,7.0982,3.7054,4.9650</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:39:14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.817117383127361</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="H42" t="n">
+        <v>41</v>
+      </c>
+      <c r="I42" t="n">
+        <v>56.0449</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0:56.04</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>54.6365</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.2496</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2295.5517</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>38:15.55</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:30;6:1;8:32;1:5;4:29;5:35;7:39;3:23;9:30;0:1</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[4,6];6:[];8:[3,4,6];1:[];4:[1,4];5:[3,4,6];7:[0,4,6];3:[4];9:[1,4,6];0:[]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[4,6]; c6:bw=1,experts=[]; c8:bw=32,experts=[3,4,6]; c1:bw=5,experts=[]; c4:bw=29,experts=[1,4]; c5:bw=35,experts=[3,4,6]; c7:bw=39,experts=[0,4,6]; c3:bw=23,experts=[4]; c9:bw=30,experts=[1,4,6]; c0:bw=1,experts=[]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4.0443,7.1811,5.7158,4.6593,7.1759,6.6530,5.0225,5.4252,3.7579,5.0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:40:10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.870926230086896</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="G43" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="H43" t="n">
+        <v>41</v>
+      </c>
+      <c r="I43" t="n">
+        <v>56.111</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0:56.11</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>54.6927</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.2736</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2351.6901</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>39:11.69</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:29;1:28;3:27;9:29;6:19;0:8;7:11;4:31;8:24;2:23</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[2];1:[0,6];3:[0,1];9:[3,5];6:[3];0:[];7:[1];4:[3,4,6];8:[4,6];2:[1,2]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[2]; c1:bw=28,experts=[0,6]; c3:bw=27,experts=[0,1]; c9:bw=29,experts=[3,5]; c6:bw=19,experts=[3]; c0:bw=8,experts=[]; c7:bw=11,experts=[1]; c4:bw=31,experts=[3,4,6]; c8:bw=24,experts=[4,6]; c2:bw=23,experts=[1,2]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>6.7163,4.6519,5.5801,3.7096,6.6273,5.0926,4.9069,7.4850,5.8890,4.0340</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:41:05</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.870133234429675</v>
+      </c>
+      <c r="F44" t="n">
+        <v>44.09</v>
+      </c>
+      <c r="G44" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="H44" t="n">
+        <v>41</v>
+      </c>
+      <c r="I44" t="n">
+        <v>54.6183</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0:54.62</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>53.1978</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2406.3353</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>40:06.34</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:30;1:33;2:29;8:26;9:18;7:12;4:19;6:7;3:37;0:12</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[4,6,7];1:[1,4,6];2:[4,6];8:[2,7];9:[7];7:[3];4:[7];6:[];3:[4,6];0:[0]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=30,experts=[4,6,7]; c1:bw=33,experts=[1,4,6]; c2:bw=29,experts=[4,6]; c8:bw=26,experts=[2,7]; c9:bw=18,experts=[7]; c7:bw=12,experts=[3]; c4:bw=19,experts=[7]; c6:bw=7,experts=[]; c3:bw=37,experts=[4,6]; c0:bw=12,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>7.0557,4.2075,3.8003,5.3192,3.4857,4.5465,7.1135,7.0867,5.5466,5.0360</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:42:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.828014105771761</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="G45" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>55.469</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0:55.47</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>54.0654</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.2497</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2461.8319</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>41:01.83</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:38;3:26;4:16;2:21;7:42;5:14;6:12;9:21;8:19;1:25</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[2,3,5];3:[3,4];4:[0];2:[4,6];7:[0,1,4,6];5:[4];6:[2];9:[4];8:[5];1:[4,6]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=38,experts=[2,3,5]; c3:bw=26,experts=[3,4]; c4:bw=16,experts=[0]; c2:bw=21,experts=[4,6]; c7:bw=42,experts=[0,1,4,6]; c5:bw=14,experts=[4]; c6:bw=12,experts=[2]; c9:bw=21,experts=[4]; c8:bw=19,experts=[5]; c1:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4.9967,5.3859,7.1323,3.9456,4.9170,6.5939,6.9911,3.6835,5.6619,4.7576</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:42:56</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.770646547055044</v>
+      </c>
+      <c r="F46" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="G46" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>55.9968</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0:56.00</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>54.5847</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.2548</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2517.8524</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>41:57.85</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:31;0:20;3:38;4:36;7:20;2:28;9:14;6:2;5:25;1:32</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[4,6];0:[4,7];3:[0,4,6];4:[2,4,5];7:[4];2:[3,4];9:[2];6:[];5:[5];1:[2,4,6]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=31,experts=[4,6]; c0:bw=20,experts=[4,7]; c3:bw=38,experts=[0,4,6]; c4:bw=36,experts=[2,4,5]; c7:bw=20,experts=[4]; c2:bw=28,experts=[3,4]; c9:bw=14,experts=[2]; c6:bw=2,experts=[]; c5:bw=25,experts=[5]; c1:bw=32,experts=[2,4,6]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5.7835,4.9849,5.4385,7.1266,4.9730,3.9494,3.6989,7.0851,6.9205,4.6242</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:43:52</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.750911713694327</v>
+      </c>
+      <c r="F47" t="n">
+        <v>54</v>
+      </c>
+      <c r="G47" t="n">
+        <v>54</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>55.8172</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0:55.82</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>54.461</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.2058</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2573.6917</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>42:53.69</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:21;3:15;6:22;1:23;4:36;5:23;2:32;8:22;0:31;7:16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[4,6];3:[2];6:[5];1:[3,4];4:[0,4,6];5:[4,6];2:[0,4,6];8:[4,6];0:[0,4,6];7:[4]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=21,experts=[4,6]; c3:bw=15,experts=[2]; c6:bw=22,experts=[5]; c1:bw=23,experts=[3,4]; c4:bw=36,experts=[0,4,6]; c5:bw=23,experts=[4,6]; c2:bw=32,experts=[0,4,6]; c8:bw=22,experts=[4,6]; c0:bw=31,experts=[0,4,6]; c7:bw=16,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>3.9089,5.4939,7.0961,4.5999,7.1812,6.7166,3.9847,5.6217,5.0242,4.8338</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:44:48</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.756290679875898</v>
+      </c>
+      <c r="F48" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="G48" t="n">
+        <v>54</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" t="n">
+        <v>56.1384</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0:56.14</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>54.7412</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1493</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.2465</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2629.8534</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>43:49.85</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:29;6:13;7:30;9:10;8:22;3:39;4:5;0:26;1:17;2:31</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[0,1];6:[7];7:[2,4,6];9:[];8:[0,4];3:[4,5,7];4:[];0:[4];1:[];2:[4,5]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[0,1]; c6:bw=13,experts=[7]; c7:bw=30,experts=[2,4,6]; c9:bw=10,experts=[]; c8:bw=22,experts=[0,4]; c3:bw=39,experts=[4,5,7]; c4:bw=5,experts=[]; c0:bw=26,experts=[4]; c1:bw=17,experts=[]; c2:bw=31,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>6.8541,7.1642,4.9545,3.7164,5.7158,5.4230,7.3089,5.0051,4.6501,3.9492</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:45:45</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.747978903339853</v>
+      </c>
+      <c r="F49" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="G49" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="H49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" t="n">
+        <v>56.4693</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0:56.47</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>55.0885</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2686.3463</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>44:46.35</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:28;8:28;4:38;2:32;9:30;6:26;5:31;7:35;0:9;3:10</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[5,7];8:[1,4];4:[0,4,6];2:[4,7];9:[0,4,6];6:[6];5:[0,4,6];7:[4,5,7];0:[];3:[]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[5,7]; c8:bw=28,experts=[1,4]; c4:bw=38,experts=[0,4,6]; c2:bw=32,experts=[4,7]; c9:bw=30,experts=[0,4,6]; c6:bw=26,experts=[6]; c5:bw=31,experts=[0,4,6]; c7:bw=35,experts=[4,5,7]; c0:bw=9,experts=[]; c3:bw=10,experts=[]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>4.6680,5.8134,7.2579,3.9834,3.7643,7.1540,6.7605,5.0558,5.0133,5.6179</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:46:41</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.735333119107298</v>
+      </c>
+      <c r="F50" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="G50" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="H50" t="n">
+        <v>48</v>
+      </c>
+      <c r="I50" t="n">
+        <v>56.6884</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0:56.69</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>55.2783</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.2621</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2743.0599</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>45:43.06</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:27;3:18;8:15;0:11;2:33;5:32;6:7;7:25;9:30;1:31</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[1];3:[4];8:[3];0:[1];2:[0,4,6];5:[3,4];6:[];7:[4,6];9:[1,4,6];1:[4,6]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=27,experts=[1]; c3:bw=18,experts=[4]; c8:bw=15,experts=[3]; c0:bw=11,experts=[1]; c2:bw=33,experts=[0,4,6]; c5:bw=32,experts=[3,4]; c6:bw=7,experts=[]; c7:bw=25,experts=[4,6]; c9:bw=30,experts=[1,4,6]; c1:bw=31,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7.3583,5.5136,5.8477,5.0919,4.0546,6.7066,7.0507,5.1170,3.8583,4.6795</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:47:37</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.701465024070708</v>
+      </c>
+      <c r="F51" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="G51" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>55.7788</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0:55.78</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>54.4577</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.1816</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2798.8642</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>46:38.86</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:18;4:4;7:19;6:38;2:36;1:37;3:22;0:16;9:15;5:18</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[4];4:[];7:[4];6:[0,1,4];2:[1,2,4];1:[0,4];3:[1,4];0:[4];9:[];5:[2]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=18,experts=[4]; c4:bw=4,experts=[]; c7:bw=19,experts=[4]; c6:bw=38,experts=[0,1,4]; c2:bw=36,experts=[1,2,4]; c1:bw=37,experts=[0,4]; c3:bw=22,experts=[1,4]; c0:bw=16,experts=[4]; c9:bw=15,experts=[]; c5:bw=18,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>5.7909,7.2788,5.0694,7.0302,3.9358,4.6097,5.3846,5.0143,3.8341,6.5101</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:48:33</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.736068439366665</v>
+      </c>
+      <c r="F52" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="G52" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>55.8649</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0:55.86</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>54.5694</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2854.7542</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>47:34.75</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:27;0:30;1:12;2:11;8:26;6:29;9:10;3:31;4:6;7:15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[4,7];0:[0,4,6];1:[1];2:[4];8:[2,7];6:[3];9:[];3:[0,4,6];4:[];7:[3]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=27,experts=[4,7]; c0:bw=30,experts=[0,4,6]; c1:bw=12,experts=[1]; c2:bw=11,experts=[4]; c8:bw=26,experts=[2,7]; c6:bw=29,experts=[3]; c9:bw=10,experts=[]; c3:bw=31,experts=[0,4,6]; c4:bw=6,experts=[]; c7:bw=15,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>6.6411,5.1377,4.8936,4.2764,5.9176,7.5256,3.8137,4.9758,6.8341,4.5538</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:49:29</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.779405695177867</v>
+      </c>
+      <c r="F53" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="G53" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>56.1598</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0:56.16</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>54.6898</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.3094</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2910.9381</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>48:30.94</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:26;8:10;5:14;7:19;1:23;4:19;9:17;6:29;2:17;3:24</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[2,3];8:[5];5:[];7:[0];1:[4,6];4:[3];9:[];6:[2];2:[4];3:[3]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[2,3]; c8:bw=10,experts=[5]; c5:bw=14,experts=[]; c7:bw=19,experts=[0]; c1:bw=23,experts=[4,6]; c4:bw=19,experts=[3]; c9:bw=17,experts=[]; c6:bw=29,experts=[2]; c2:bw=17,experts=[4]; c3:bw=24,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4.7355,5.9068,6.6643,4.8615,4.7602,7.3119,3.7536,7.1594,3.9842,5.5524</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:50:26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.746758784361604</v>
+      </c>
+      <c r="F54" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="G54" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="n">
+        <v>56.4914</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0:56.49</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>55.0799</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.2717</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2967.4599</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>49:27.46</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:12;4:16;5:25;1:33;3:27;9:35;6:20;7:25;0:22;2:29</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[];4:[7];5:[5];1:[2,4,6];3:[4];9:[3,5];6:[4,6];7:[1,4];0:[5];2:[3,4]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[]; c4:bw=16,experts=[7]; c5:bw=25,experts=[5]; c1:bw=33,experts=[2,4,6]; c3:bw=27,experts=[4]; c9:bw=35,experts=[3,5]; c6:bw=20,experts=[4,6]; c7:bw=25,experts=[1,4]; c0:bw=22,experts=[5]; c2:bw=29,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>5.7573,7.4040,6.7858,4.6604,5.5629,3.7170,7.1903,4.9255,5.0521,4.0246</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:51:22</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.712281305575909</v>
+      </c>
+      <c r="F55" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="G55" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" t="n">
+        <v>56.5711</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0:56.57</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>55.173</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.2477</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3024.0561</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>50:24.06</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:5;1:30;8:31;7:34;3:17;0:21;6:31;5:2;9:29;4:18</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[];1:[3,4,6];8:[0,4,6];7:[4,6];3:[2];0:[4,7];6:[4,5,6];5:[];9:[2,7];4:[2]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=5,experts=[]; c1:bw=30,experts=[3,4,6]; c8:bw=31,experts=[0,4,6]; c7:bw=34,experts=[4,6]; c3:bw=17,experts=[2]; c0:bw=21,experts=[4,7]; c6:bw=31,experts=[4,5,6]; c5:bw=2,experts=[]; c9:bw=29,experts=[2,7]; c4:bw=18,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4.1055,4.7071,5.8313,4.8945,5.4609,5.1276,7.3576,6.6668,3.7381,7.2836</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:52:19</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.6623138156682</v>
+      </c>
+      <c r="F56" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="G56" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="n">
+        <v>56.4613</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0:56.46</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>55.0574</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3080.5495</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>51:20.55</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:31;2:23;4:8;3:30;8:8;5:30;1:34;6:24;0:16;9:35</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[2,4,6];2:[4,5];4:[];3:[4,5,7];8:[];5:[1,4,6];1:[0,4,6];6:[7];0:[4];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=31,experts=[2,4,6]; c2:bw=23,experts=[4,5]; c4:bw=8,experts=[]; c3:bw=30,experts=[4,5,7]; c8:bw=8,experts=[]; c5:bw=30,experts=[1,4,6]; c1:bw=34,experts=[0,4,6]; c6:bw=24,experts=[7]; c0:bw=16,experts=[4]; c9:bw=35,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>5.0184,4.0357,7.2723,5.5240,5.7355,6.7429,4.7659,7.1696,5.0248,3.7683</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:53:15</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.688083087506003</v>
+      </c>
+      <c r="F57" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="G57" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="H57" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" t="n">
+        <v>56.4202</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0:56.42</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>55.0188</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.2429</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3137.0008</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>52:17.00</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:29;1:32;3:5;2:30;5:17;4:5;8:8;7:10;6:13;0:40</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[0,4];1:[5,7];3:[];2:[4,6,7];5:[0];4:[];8:[];7:[5];6:[4];0:[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[0,4]; c1:bw=32,experts=[5,7]; c3:bw=5,experts=[]; c2:bw=30,experts=[4,6,7]; c5:bw=17,experts=[0]; c4:bw=5,experts=[]; c8:bw=8,experts=[]; c7:bw=10,experts=[5]; c6:bw=13,experts=[4]; c0:bw=40,experts=[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>3.7791,4.7461,5.5412,4.0044,6.7136,7.3521,5.7113,4.9647,7.1308,5.0755</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:54:12</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.678350768620757</v>
+      </c>
+      <c r="F58" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="G58" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="H58" t="n">
+        <v>57</v>
+      </c>
+      <c r="I58" t="n">
+        <v>56.642</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0:56.64</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>55.1942</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.3039</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3193.6734</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>53:13.67</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:36;8:24;6:27;1:28;7:39;0:40;5:25;4:23;2:19;9:11</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[4,6];8:[1,3];6:[4];1:[4,6];7:[4,7];0:[0,1,4,6];5:[3,4];4:[0,5];2:[0];9:[]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=36,experts=[4,6]; c8:bw=24,experts=[1,3]; c6:bw=27,experts=[4]; c1:bw=28,experts=[4,6]; c7:bw=39,experts=[4,7]; c0:bw=40,experts=[0,1,4,6]; c5:bw=25,experts=[3,4]; c4:bw=23,experts=[0,5]; c2:bw=19,experts=[0]; c9:bw=11,experts=[]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>5.5709,5.7760,7.3373,4.7123,4.9516,5.0609,6.6489,7.3844,3.9760,3.7759</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:55:08</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.631003387018231</v>
+      </c>
+      <c r="F59" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="G59" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H59" t="n">
+        <v>58</v>
+      </c>
+      <c r="I59" t="n">
+        <v>56.2642</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0:56.26</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>54.853</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.2624</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3249.9649</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>54:09.96</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:14;2:2;9:32;6:31;5:20;1:17;8:22;4:22;3:35;0:27</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[4];2:[];9:[1,4,6];6:[0,1,4];5:[2,4];1:[4];8:[4];4:[4,6];3:[1,4];0:[4]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=14,experts=[4]; c2:bw=2,experts=[]; c9:bw=32,experts=[1,4,6]; c6:bw=31,experts=[0,1,4]; c5:bw=20,experts=[2,4]; c1:bw=17,experts=[4]; c8:bw=22,experts=[4]; c4:bw=22,experts=[4,6]; c3:bw=35,experts=[1,4]; c0:bw=27,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>4.9865,4.0157,3.7862,7.2420,6.6189,4.6160,5.6221,7.2980,5.6070,5.0606</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:56:05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.650844626306987</v>
+      </c>
+      <c r="F60" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="G60" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H60" t="n">
+        <v>58</v>
+      </c>
+      <c r="I60" t="n">
+        <v>57.2475</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0:57.25</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>55.7607</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.3368</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3307.2427</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>55:07.24</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:21;8:31;9:16;6:11;1:37;4:15;7:16;5:18;0:29;3:20</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[1,2];8:[2,4,7];9:[4];6:[3];1:[1,4,6];4:[];7:[3];5:[7];0:[4,6];3:[0,4]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=21,experts=[1,2]; c8:bw=31,experts=[2,4,7]; c9:bw=16,experts=[4]; c6:bw=11,experts=[3]; c1:bw=37,experts=[1,4,6]; c4:bw=15,experts=[]; c7:bw=16,experts=[3]; c5:bw=18,experts=[7]; c0:bw=29,experts=[4,6]; c3:bw=20,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>4.1330,5.8236,3.7737,7.2364,4.4232,7.2078,5.0520,7.0532,5.3578,5.6999</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:57:01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.649949705109165</v>
+      </c>
+      <c r="F61" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="G61" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H61" t="n">
+        <v>58</v>
+      </c>
+      <c r="I61" t="n">
+        <v>55.2691</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0:55.27</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>53.8543</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1421</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.2712</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3362.5437</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>56:02.54</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:30;7:27;4:17;2:17;5:19;8:14;6:34;9:4;1:31;3:25</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[2,3,4];7:[0];4:[1];2:[];5:[];8:[];6:[2,4,6];9:[];1:[0,4,6];3:[3,4]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=30,experts=[2,3,4]; c7:bw=27,experts=[0]; c4:bw=17,experts=[1]; c2:bw=17,experts=[]; c5:bw=19,experts=[]; c8:bw=14,experts=[]; c6:bw=34,experts=[2,4,6]; c9:bw=4,experts=[]; c1:bw=31,experts=[0,4,6]; c3:bw=25,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>5.3656,4.6153,6.8453,3.7215,6.3874,5.6183,7.2500,3.7657,4.7166,5.5685</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:57:57</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.637755314044739</v>
+      </c>
+      <c r="F62" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="G62" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H62" t="n">
+        <v>58</v>
+      </c>
+      <c r="I62" t="n">
+        <v>56.4584</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0:56.46</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>54.9756</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.3286</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3419.0305</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>56:59.03</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:28;6:21;2:16;9:21;1:19;3:24;8:31;4:22;7:25;0:34</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[4,5];6:[4,6];2:[];9:[3];1:[];3:[4];8:[4,5,6];4:[3,7];7:[1,4];0:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=28,experts=[4,5]; c6:bw=21,experts=[4,6]; c2:bw=16,experts=[]; c9:bw=21,experts=[3]; c1:bw=19,experts=[]; c3:bw=24,experts=[4]; c8:bw=31,experts=[4,5,6]; c4:bw=22,experts=[3,7]; c7:bw=25,experts=[1,4]; c0:bw=34,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>6.7132,7.2466,4.0059,3.7673,4.7105,5.5963,5.7427,7.2317,4.9029,5.0585</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:58:54</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.633664913753198</v>
+      </c>
+      <c r="F63" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="G63" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H63" t="n">
+        <v>58</v>
+      </c>
+      <c r="I63" t="n">
+        <v>56.7205</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0:56.72</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>55.2874</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.2473</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3475.7818</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>57:55.78</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:7;6:35;9:9;4:34;5:38;0:16;3:30;2:24;1:42;7:25</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[];6:[4,5,6];9:[];4:[2,4,6];5:[0,4,6];0:[7];3:[2,4,6];2:[3];1:[2,3,4,6];7:[4,6]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=7,experts=[]; c6:bw=35,experts=[4,5,6]; c9:bw=9,experts=[]; c4:bw=34,experts=[2,4,6]; c5:bw=38,experts=[0,4,6]; c0:bw=16,experts=[7]; c3:bw=30,experts=[2,4,6]; c2:bw=24,experts=[3]; c1:bw=42,experts=[2,3,4,6]; c7:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>5.7869,7.1461,3.8114,7.2762,6.8004,5.0473,5.6806,4.1539,4.6062,4.9784</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:59:50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.63070368848319</v>
+      </c>
+      <c r="F64" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="G64" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H64" t="n">
+        <v>58</v>
+      </c>
+      <c r="I64" t="n">
+        <v>56.3225</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0:56.32</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>54.887</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.2998</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3532.138</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>58:52.14</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:5;9:12;6:19;3:30;8:18;1:28;7:39;0:23;2:16;4:30</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[];9:[5];6:[7];3:[4,5,7];8:[0];1:[4];7:[2,4];0:[4,6];2:[5];4:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=5,experts=[]; c9:bw=12,experts=[5]; c6:bw=19,experts=[7]; c3:bw=30,experts=[4,5,7]; c8:bw=18,experts=[0]; c1:bw=28,experts=[4]; c7:bw=39,experts=[2,4]; c0:bw=23,experts=[4,6]; c2:bw=16,experts=[5]; c4:bw=30,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>6.8925,3.7585,7.0764,5.4728,5.7230,4.7457,4.9619,5.0782,3.9515,7.2265</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:00:47</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.619067999143089</v>
+      </c>
+      <c r="F65" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="G65" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="H65" t="n">
+        <v>58</v>
+      </c>
+      <c r="I65" t="n">
+        <v>56.5429</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0:56.54</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>55.1303</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.2759</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3588.7087</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>59:48.71</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:28;4:21;5:13;3:21;7:19;0:18;8:30;9:34;2:32;1:16</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[4,6];4:[4,6];5:[1];3:[4,6];7:[5];0:[5];8:[0,4,6];9:[0,2,7];2:[4,6,7];1:[]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=28,experts=[4,6]; c4:bw=21,experts=[4,6]; c5:bw=13,experts=[1]; c3:bw=21,experts=[4,6]; c7:bw=19,experts=[5]; c0:bw=18,experts=[5]; c8:bw=30,experts=[0,4,6]; c9:bw=34,experts=[0,2,7]; c2:bw=32,experts=[4,6,7]; c1:bw=16,experts=[]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>7.2369,7.3140,6.8949,5.5644,4.9318,5.0520,5.7463,3.7395,4.0206,4.6298</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:01:43</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.604925296738897</v>
+      </c>
+      <c r="F66" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="G66" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="H66" t="n">
+        <v>65</v>
+      </c>
+      <c r="I66" t="n">
+        <v>56.1753</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0:56.18</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>54.7698</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1328</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.2715</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3644.9119</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:00:44.91</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:5;5:16;4:32;6:28;8:37;3:24;0:23;2:16;1:33;9:26</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[];5:[3];4:[4,5];6:[4];8:[1,3,4];3:[4];0:[1,4];2:[0];1:[4,5,7];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=5,experts=[]; c5:bw=16,experts=[3]; c4:bw=32,experts=[4,5]; c6:bw=28,experts=[4]; c8:bw=37,experts=[1,3,4]; c3:bw=24,experts=[4]; c0:bw=23,experts=[1,4]; c2:bw=16,experts=[0]; c1:bw=33,experts=[4,5,7]; c9:bw=26,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>4.8926,6.8094,7.1737,7.0605,5.6895,5.4930,5.1932,3.9888,4.6749,3.7942</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:02:40</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.583933264008169</v>
+      </c>
+      <c r="F67" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="G67" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="H67" t="n">
+        <v>66</v>
+      </c>
+      <c r="I67" t="n">
+        <v>56.5516</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0:56.55</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>55.1108</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1368</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.3027</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3701.4911</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:01:41.49</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:23;5:10;1:31;8:14;9:18;6:17;4:23;0:21;3:38;7:28</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[4,6];5:[2];1:[0,4,6];8:[4];9:[1];6:[];4:[4];0:[4,6];3:[1,4,6];7:[4,7]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=23,experts=[4,6]; c5:bw=10,experts=[2]; c1:bw=31,experts=[0,4,6]; c8:bw=14,experts=[4]; c9:bw=18,experts=[1]; c6:bw=17,experts=[]; c4:bw=23,experts=[4]; c0:bw=21,experts=[4,6]; c3:bw=38,experts=[1,4,6]; c7:bw=28,experts=[4,7]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>4.0305,6.7739,4.8338,5.7595,3.7738,7.0727,7.1567,5.2106,5.5533,4.9461</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:03:36</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.575298577554339</v>
+      </c>
+      <c r="F68" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="G68" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="H68" t="n">
+        <v>66</v>
+      </c>
+      <c r="I68" t="n">
+        <v>56.2283</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0:56.23</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>54.7748</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.3068</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3757.7491</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:02:37.75</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:29;5:27;1:21;3:14;6:30;0:18;2:24;9:34;7:33;8:5</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[4,6];5:[4,7];1:[1,4];3:[0];6:[0,1,3];0:[4];2:[1,2];9:[4,6];7:[3,4,6];8:[]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=29,experts=[4,6]; c5:bw=27,experts=[4,7]; c1:bw=21,experts=[1,4]; c3:bw=14,experts=[0]; c6:bw=30,experts=[0,1,3]; c0:bw=18,experts=[4]; c2:bw=24,experts=[1,2]; c9:bw=34,experts=[4,6]; c7:bw=33,experts=[3,4,6]; c8:bw=5,experts=[]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>7.4367,6.7298,4.8754,5.4905,7.1407,5.1030,4.0033,3.7581,4.9548,5.2824</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:04:33</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.599936517246161</v>
+      </c>
+      <c r="F69" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="G69" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="H69" t="n">
+        <v>66</v>
+      </c>
+      <c r="I69" t="n">
+        <v>56.5943</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0:56.59</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>55.2566</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.1995</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3814.38</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:03:34.38</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:24;8:18;2:33;0:17;3:15;4:28;5:25;9:9;7:16;6:18</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[4,6];8:[2];2:[0,4,6];0:[2];3:[];4:[1];5:[4,6];9:[];7:[];6:[2]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=24,experts=[4,6]; c8:bw=18,experts=[2]; c2:bw=33,experts=[0,4,6]; c0:bw=17,experts=[2]; c3:bw=15,experts=[]; c4:bw=28,experts=[1]; c5:bw=25,experts=[4,6]; c9:bw=9,experts=[]; c7:bw=16,experts=[]; c6:bw=18,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>4.9424,5.9826,4.2464,5.5024,5.9666,7.5965,6.2144,3.5309,4.5515,6.7228</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:05:29</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.589301854483212</v>
+      </c>
+      <c r="F70" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="G70" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H70" t="n">
+        <v>69</v>
+      </c>
+      <c r="I70" t="n">
+        <v>56.899</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0:56.90</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>55.4379</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3871.3087</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:04:31.31</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:23;7:33;1:18;4:23;9:20;5:22;0:30;2:38;8:24;6:15</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[3];7:[0,1,4];1:[4];4:[3,7];9:[3,4];5:[4,5];0:[0,3,4];2:[0,4,6];8:[5,7];6:[]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=23,experts=[3]; c7:bw=33,experts=[0,1,4]; c1:bw=18,experts=[4]; c4:bw=23,experts=[3,7]; c9:bw=20,experts=[3,4]; c5:bw=22,experts=[4,5]; c0:bw=30,experts=[0,3,4]; c2:bw=38,experts=[0,4,6]; c8:bw=24,experts=[5,7]; c6:bw=15,experts=[]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>5.6384,5.0184,4.6986,7.3592,3.9036,6.6752,5.0965,4.0594,5.7701,7.2184</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:06:26</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.585940679872729</v>
+      </c>
+      <c r="F71" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G71" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H71" t="n">
+        <v>69</v>
+      </c>
+      <c r="I71" t="n">
+        <v>56.3386</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0:56.34</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>54.9305</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3927.683</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:05:27.68</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:14;9:1;7:16;3:18;0:17;6:15;2:31;4:33;5:13;8:27</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[2];9:[];7:[];3:[2];0:[7];6:[5];2:[3,4,6];4:[2,4,6];5:[0];8:[4]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=14,experts=[2]; c9:bw=1,experts=[]; c7:bw=16,experts=[]; c3:bw=18,experts=[2]; c0:bw=17,experts=[7]; c6:bw=15,experts=[5]; c2:bw=31,experts=[3,4,6]; c4:bw=33,experts=[2,4,6]; c5:bw=13,experts=[0]; c8:bw=27,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>4.6536,3.8459,4.9568,5.4760,5.0210,7.2063,4.0133,7.2694,6.7947,5.6934</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:07:24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.575123732422918</v>
+      </c>
+      <c r="F72" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="G72" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H72" t="n">
+        <v>69</v>
+      </c>
+      <c r="I72" t="n">
+        <v>57.6539</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0:57.65</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>56.259</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.2289</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3985.3738</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:06:25.37</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:24;0:9;1:30;9:23;7:12;5:19;3:35;6:28;8:22;2:34</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[0,4];0:[];1:[3,4,6];9:[4,5];7:[];5:[4];3:[4,5,7];6:[7];8:[4,6];2:[4,5]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=24,experts=[0,4]; c0:bw=9,experts=[]; c1:bw=30,experts=[3,4,6]; c9:bw=23,experts=[4,5]; c7:bw=12,experts=[]; c5:bw=19,experts=[4]; c3:bw=35,experts=[4,5,7]; c6:bw=28,experts=[7]; c8:bw=22,experts=[4,6]; c2:bw=34,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>7.4463,5.1295,4.7703,3.9141,5.0068,7.0545,5.7179,7.4216,5.8227,3.9752</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:08:20</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.578681533934358</v>
+      </c>
+      <c r="F73" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="G73" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H73" t="n">
+        <v>69</v>
+      </c>
+      <c r="I73" t="n">
+        <v>56.5807</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0:56.58</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>55.1641</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.2718</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4041.9853</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:07:21.99</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:17;1:22;5:24;7:27;6:11;0:30;3:13;2:13;9:21;4:22</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[0];1:[4,6];5:[1,4];7:[2,5];6:[6];0:[4,5,6];3:[4];2:[];9:[0,2];4:[4]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=17,experts=[0]; c1:bw=22,experts=[4,6]; c5:bw=24,experts=[1,4]; c7:bw=27,experts=[2,5]; c6:bw=11,experts=[6]; c0:bw=30,experts=[4,5,6]; c3:bw=13,experts=[4]; c2:bw=13,experts=[]; c9:bw=21,experts=[0,2]; c4:bw=22,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>5.8909,4.8272,6.7037,4.9073,7.0993,5.2207,5.4882,3.9765,3.8011,7.2493</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:09:17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.548700964237216</v>
+      </c>
+      <c r="F74" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="G74" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H74" t="n">
+        <v>69</v>
+      </c>
+      <c r="I74" t="n">
+        <v>56.3425</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0:56.34</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>54.9467</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.2375</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4098.3583</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:08:18.36</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:27;8:6;3:22;1:37;5:10;9:29;0:16;7:21;6:11;4:23</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[4,7];8:[];3:[4,6];1:[5,7];5:[3];9:[4,7];0:[1];7:[4,6];6:[];4:[4,5]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=27,experts=[4,7]; c8:bw=6,experts=[]; c3:bw=22,experts=[4,6]; c1:bw=37,experts=[5,7]; c5:bw=10,experts=[3]; c9:bw=29,experts=[4,7]; c0:bw=16,experts=[1]; c7:bw=21,experts=[4,6]; c6:bw=11,experts=[]; c4:bw=23,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>4.0205,5.8703,5.5093,4.7093,6.7967,3.7511,5.0229,5.0414,7.0027,7.2224</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:10:13</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.55465322341025</v>
+      </c>
+      <c r="F75" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H75" t="n">
+        <v>69</v>
+      </c>
+      <c r="I75" t="n">
+        <v>56.4075</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0:56.41</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>55.0114</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.2633</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4154.8023</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:09:14.80</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:4;0:22;1:16;5:28;7:37;8:16;6:5;2:3;4:27;9:18</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[];0:[4,6];1:[0];5:[2,4];7:[4,6,7];8:[1];6:[];2:[];4:[4];9:[]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=4,experts=[]; c0:bw=22,experts=[4,6]; c1:bw=16,experts=[0]; c5:bw=28,experts=[2,4]; c7:bw=37,experts=[4,6,7]; c8:bw=16,experts=[1]; c6:bw=5,experts=[]; c2:bw=3,experts=[]; c4:bw=27,experts=[4]; c9:bw=18,experts=[]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>5.5626,5.2360,4.7357,6.6625,4.9470,5.7355,7.0442,4.0837,7.2349,3.7692</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:11:09</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.554929082830187</v>
+      </c>
+      <c r="F76" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="G76" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H76" t="n">
+        <v>69</v>
+      </c>
+      <c r="I76" t="n">
+        <v>56.4762</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0:56.48</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>55.0526</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.2854</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4211.31</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:10:11.31</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:22;9:35;1:31;3:11;7:16;6:32;5:18;4:32;0:34;8:30</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[1,2];9:[1,6];1:[1,4,6];3:[1];7:[3];6:[0,4];5:[7];4:[4,6];0:[0,4,6];8:[3,4,6]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=22,experts=[1,2]; c9:bw=35,experts=[1,6]; c1:bw=31,experts=[1,4,6]; c3:bw=11,experts=[1]; c7:bw=16,experts=[3]; c6:bw=32,experts=[0,4]; c5:bw=18,experts=[7]; c4:bw=32,experts=[4,6]; c0:bw=34,experts=[0,4,6]; c8:bw=30,experts=[3,4,6]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>4.0092,3.8057,4.6811,5.5941,4.9597,7.0954,6.7247,7.2164,5.2132,5.7531</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:12:07</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.526749389341532</v>
+      </c>
+      <c r="F77" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="G77" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H77" t="n">
+        <v>69</v>
+      </c>
+      <c r="I77" t="n">
+        <v>57.9218</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0:57.92</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>56.6474</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.1392</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4269.2621</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:11:09.26</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:16;5:21;0:18;3:8;2:14;6:13;7:38;4:34;9:32;1:30</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[];5:[4,6];0:[];3:[];2:[4];6:[1];7:[0,4,6];4:[1,4,6];9:[0,4,6];1:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=16,experts=[]; c5:bw=21,experts=[4,6]; c0:bw=18,experts=[]; c3:bw=8,experts=[]; c2:bw=14,experts=[4]; c6:bw=13,experts=[1]; c7:bw=38,experts=[0,4,6]; c4:bw=34,experts=[1,4,6]; c9:bw=32,experts=[0,4,6]; c1:bw=30,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>5.7754,6.7911,4.7961,5.5326,4.0794,7.4499,5.2838,7.9356,4.3393,4.6643</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:13:03</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.541193180274837</v>
+      </c>
+      <c r="F78" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="G78" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="H78" t="n">
+        <v>77</v>
+      </c>
+      <c r="I78" t="n">
+        <v>55.7484</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0:55.75</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>54.3403</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.2439</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4325.0416</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:12:05.04</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:16;2:19;1:35;8:1;4:2;7:5;6:32;0:36;3:23;5:34</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[3];2:[0];1:[0,4,6];8:[];4:[];7:[];6:[2,3,4];0:[2,3,4];3:[0,3];5:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=16,experts=[3]; c2:bw=19,experts=[0]; c1:bw=35,experts=[0,4,6]; c8:bw=1,experts=[]; c4:bw=2,experts=[]; c7:bw=5,experts=[]; c6:bw=32,experts=[2,3,4]; c0:bw=36,experts=[2,3,4]; c3:bw=23,experts=[0,3]; c5:bw=34,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>3.5537,3.8036,4.4140,5.5318,7.3142,4.9107,7.1269,5.0758,5.6579,6.9517</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:14:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.526853668601528</v>
+      </c>
+      <c r="F79" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="G79" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="H79" t="n">
+        <v>78</v>
+      </c>
+      <c r="I79" t="n">
+        <v>56.9752</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0:56.98</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>55.5635</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.2484</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4382.0504</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:13:02.05</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:15;4:13;3:21;7:21;8:31;1:23;9:17;6:33;5:36;2:20</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[];4:[];3:[2,4];7:[1,4];8:[2,5,7];1:[2];9:[4];6:[4,5,6];5:[0,4,6];2:[3,6]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=15,experts=[]; c4:bw=13,experts=[]; c3:bw=21,experts=[2,4]; c7:bw=21,experts=[1,4]; c8:bw=31,experts=[2,5,7]; c1:bw=23,experts=[2]; c9:bw=17,experts=[4]; c6:bw=33,experts=[4,5,6]; c5:bw=36,experts=[0,4,6]; c2:bw=20,experts=[3,6]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>5.2121,7.3150,5.5115,4.9433,5.8917,4.7409,3.8217,7.1983,6.8100,4.1188</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:14:57</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.51885171172256</v>
+      </c>
+      <c r="F80" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="G80" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="H80" t="n">
+        <v>79</v>
+      </c>
+      <c r="I80" t="n">
+        <v>56.918</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0:56.92</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>55.4629</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.2945</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4439.003</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:13:59.00</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:12;9:5;0:20;4:48;7:26;8:25;5:30;3:15;1:21;2:19</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[7];9:[];0:[4,7];4:[0,2,3,7];7:[4,6];8:[4,6];5:[0,4,6];3:[5];1:[3,4];2:[5]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=12,experts=[7]; c9:bw=5,experts=[]; c0:bw=20,experts=[4,7]; c4:bw=48,experts=[0,2,3,7]; c7:bw=26,experts=[4,6]; c8:bw=25,experts=[4,6]; c5:bw=30,experts=[0,4,6]; c3:bw=15,experts=[5]; c1:bw=21,experts=[3,4]; c2:bw=19,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>7.2324,3.8260,5.2001,7.2866,5.0336,5.7814,6.8337,5.4999,4.7430,4.0261</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:15:54</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.507567824220093</v>
+      </c>
+      <c r="F81" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="G81" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="H81" t="n">
+        <v>79</v>
+      </c>
+      <c r="I81" t="n">
+        <v>57.2272</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0:57.23</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>55.8013</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4496.265</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:14:56.26</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:37;9:30;7:27;1:17;3:18;4:32;2:25;0:27;6:22;8:29</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[1,4,6];9:[2,4,5];7:[2,5];1:[4];3:[7];4:[4,6];2:[4,6];0:[4,5];6:[4];8:[0]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=37,experts=[1,4,6]; c9:bw=30,experts=[2,4,5]; c7:bw=27,experts=[2,5]; c1:bw=17,experts=[4]; c3:bw=18,experts=[7]; c4:bw=32,experts=[4,6]; c2:bw=25,experts=[4,6]; c0:bw=27,experts=[4,5]; c6:bw=22,experts=[4]; c8:bw=29,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>7.2042,3.8176,4.9890,4.7507,5.5195,7.4466,4.0821,5.1199,7.1369,5.7347</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:16:52</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.497926007055685</v>
+      </c>
+      <c r="F82" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="G82" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="H82" t="n">
+        <v>81</v>
+      </c>
+      <c r="I82" t="n">
+        <v>57.0886</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0:57.09</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>55.6591</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.2889</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4553.3889</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:15:53.39</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:29;2:25;3:38;1:28;4:24;5:17;9:15;7:33;8:27;0:28</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[4,6];2:[7];3:[4,6];1:[5,7];4:[4,5];5:[];9:[];7:[0,4,6];8:[4];0:[1,4]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[4,6]; c2:bw=25,experts=[7]; c3:bw=38,experts=[4,6]; c1:bw=28,experts=[5,7]; c4:bw=24,experts=[4,5]; c5:bw=17,experts=[]; c9:bw=15,experts=[]; c7:bw=33,experts=[0,4,6]; c8:bw=27,experts=[4]; c0:bw=28,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>7.3600,4.0459,5.5917,4.7692,7.3579,6.9637,3.7519,4.9379,5.7489,5.1319</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:17:49</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.467639340695856</v>
+      </c>
+      <c r="F83" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="G83" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="H83" t="n">
+        <v>82</v>
+      </c>
+      <c r="I83" t="n">
+        <v>56.9822</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0:56.98</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>55.542</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.2982</v>
+      </c>
+      <c r="N83" t="n">
+        <v>4610.613</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:16:50.61</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:36;0:17;6:21;8:33;7:23;3:22;2:17;9:32;5:23;4:17</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[4,6];0:[4];6:[4,6];8:[1,4,6];7:[4,7];3:[4];2:[4];9:[4,6,7];5:[2,3];4:[4]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=36,experts=[4,6]; c0:bw=17,experts=[4]; c6:bw=21,experts=[4,6]; c8:bw=33,experts=[1,4,6]; c7:bw=23,experts=[4,7]; c3:bw=22,experts=[4]; c2:bw=17,experts=[4]; c9:bw=32,experts=[4,6,7]; c5:bw=23,experts=[2,3]; c4:bw=17,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>4.7597,5.2812,7.2272,5.8206,4.9624,5.5228,4.1402,3.7887,6.8035,7.2356</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:18:46</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.483343035434846</v>
+      </c>
+      <c r="F84" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="G84" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H84" t="n">
+        <v>83</v>
+      </c>
+      <c r="I84" t="n">
+        <v>56.9941</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0:56.99</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>55.5762</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.2823</v>
+      </c>
+      <c r="N84" t="n">
+        <v>4667.6423</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:17:47.64</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:29;4:6;2:23;7:21;5:1;0:1;6:30;1:36;8:22;3:24</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[1,4];4:[];2:[1,2];7:[3,4];5:[];0:[];6:[0,4,6];1:[1,4];8:[3,4];3:[1,4]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[1,4]; c4:bw=6,experts=[]; c2:bw=23,experts=[1,2]; c7:bw=21,experts=[3,4]; c5:bw=1,experts=[]; c0:bw=1,experts=[]; c6:bw=30,experts=[0,4,6]; c1:bw=36,experts=[1,4]; c8:bw=22,experts=[3,4]; c3:bw=24,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>3.7690,7.4201,4.0039,4.9447,6.8224,5.1555,7.3165,4.7243,5.8509,5.5688</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:19:43</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.487364510886184</v>
+      </c>
+      <c r="F85" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H85" t="n">
+        <v>83</v>
+      </c>
+      <c r="I85" t="n">
+        <v>57.1523</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0:57.15</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>55.6325</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4725.033</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:18:45.03</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:38;3:18;1:33;6:2;9:12;2:21;7:27;5:11;4:16;0:6</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[0,4,6];3:[4];1:[4,6];6:[];9:[0];2:[4];7:[4,6];5:[7];4:[1];0:[]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=38,experts=[0,4,6]; c3:bw=18,experts=[4]; c1:bw=33,experts=[4,6]; c6:bw=2,experts=[]; c9:bw=12,experts=[0]; c2:bw=21,experts=[4]; c7:bw=27,experts=[4,6]; c5:bw=11,experts=[7]; c4:bw=16,experts=[1]; c0:bw=6,experts=[]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>5.8669,5.6945,4.8059,7.2304,3.8445,4.0741,4.9828,6.3716,7.4147,5.3471</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:20:40</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.47838798767668</v>
+      </c>
+      <c r="F86" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="G86" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H86" t="n">
+        <v>83</v>
+      </c>
+      <c r="I86" t="n">
+        <v>56.4987</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0:56.50</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>55.0711</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.2774</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4781.5729</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:19:41.57</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:22;2:26;8:40;6:24;1:32;4:24;9:33;3:29;5:7;7:6</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[0,6];2:[0,4];8:[0,4,5,6];6:[1,2];1:[0,4];4:[4,6];9:[3,4,6];3:[0,3];5:[];7:[]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=22,experts=[0,6]; c2:bw=26,experts=[0,4]; c8:bw=40,experts=[0,4,5,6]; c6:bw=24,experts=[1,2]; c1:bw=32,experts=[0,4]; c4:bw=24,experts=[4,6]; c9:bw=33,experts=[3,4,6]; c3:bw=29,experts=[0,3]; c5:bw=7,experts=[]; c7:bw=6,experts=[]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>5.4737,4.3055,6.2907,7.2517,4.3219,6.8664,3.5605,5.2263,6.8109,4.9634</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:21:37</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.496453247714515</v>
+      </c>
+      <c r="F87" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H87" t="n">
+        <v>83</v>
+      </c>
+      <c r="I87" t="n">
+        <v>57.1485</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0:57.15</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>55.7013</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.3099</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4838.7534</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:20:38.75</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:27;8:16;2:14;6:31;0:17;4:10;7:25;3:16;1:41;9:24</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[5];8:[2];2:[3];6:[3,5];0:[2];4:[4];7:[1];3:[2];1:[2,4,6];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=27,experts=[5]; c8:bw=16,experts=[2]; c2:bw=14,experts=[3]; c6:bw=31,experts=[3,5]; c0:bw=17,experts=[2]; c4:bw=10,experts=[4]; c7:bw=25,experts=[1]; c3:bw=16,experts=[2]; c1:bw=41,experts=[2,4,6]; c9:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>6.9767,5.8451,4.1430,7.2001,5.1290,7.2945,4.9243,5.5358,4.8422,3.8105</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:22:34</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.468591144330746</v>
+      </c>
+      <c r="F88" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="G88" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H88" t="n">
+        <v>83</v>
+      </c>
+      <c r="I88" t="n">
+        <v>56.7921</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0:56.79</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>55.3671</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.2856</v>
+      </c>
+      <c r="N88" t="n">
+        <v>4895.5796</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:21:35.58</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:16;2:38;7:12;5:2;6:34;3:38;4:19;9:21;8:26;0:20</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[];2:[4,5,6];7:[4];5:[];6:[4,7];3:[4,5,6];4:[];9:[4];8:[7];0:[3,7]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=16,experts=[]; c2:bw=38,experts=[4,5,6]; c7:bw=12,experts=[4]; c5:bw=2,experts=[]; c6:bw=34,experts=[4,7]; c3:bw=38,experts=[4,5,6]; c4:bw=19,experts=[]; c9:bw=21,experts=[4]; c8:bw=26,experts=[7]; c0:bw=20,experts=[3,7]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>4.7196,4.0360,5.0008,6.8911,7.1669,5.5183,7.2958,3.7643,5.7871,5.1873</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:23:31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.471185352965074</v>
+      </c>
+      <c r="F89" t="n">
+        <v>61.42</v>
+      </c>
+      <c r="G89" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H89" t="n">
+        <v>83</v>
+      </c>
+      <c r="I89" t="n">
+        <v>57.2207</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0:57.22</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>55.7978</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.2627</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4952.8346</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:22:32.83</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:24;6:15;3:19;7:23;0:35;4:21;9:17;1:16;5:17;2:26</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[4];3:[7];7:[2,5];0:[4,5];4:[0,2];9:[2];1:[3];5:[0];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=24,experts=[4,6]; c6:bw=15,experts=[4]; c3:bw=19,experts=[7]; c7:bw=23,experts=[2,5]; c0:bw=35,experts=[4,5]; c4:bw=21,experts=[0,2]; c9:bw=17,experts=[2]; c1:bw=16,experts=[3]; c5:bw=17,experts=[0]; c2:bw=26,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>5.8195,7.2593,5.5308,5.0246,5.2200,7.3081,3.7989,4.7295,6.9367,4.1704</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:24:28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.47363547785171</v>
+      </c>
+      <c r="F90" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="G90" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="H90" t="n">
+        <v>83</v>
+      </c>
+      <c r="I90" t="n">
+        <v>56.9148</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0:56.91</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>55.3807</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.3799</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5009.7861</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:23:29.79</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:17;8:42;2:25;9:34;7:12;5:26;0:7;6:18;4:17;1:23</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[];8:[0,4,5,6];2:[4,7];9:[4,5,6];7:[];5:[1,4];0:[];6:[4];4:[];1:[5,7]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=17,experts=[]; c8:bw=42,experts=[0,4,5,6]; c2:bw=25,experts=[4,7]; c9:bw=34,experts=[4,5,6]; c7:bw=12,experts=[]; c5:bw=26,experts=[1,4]; c0:bw=7,experts=[]; c6:bw=18,experts=[4]; c4:bw=17,experts=[]; c1:bw=23,experts=[5,7]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>5.6073,5.8913,4.0489,3.7769,4.9223,6.8649,5.0368,7.1788,7.3090,4.7443</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:25:26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.442868781285701</v>
+      </c>
+      <c r="F91" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="G91" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H91" t="n">
+        <v>90</v>
+      </c>
+      <c r="I91" t="n">
+        <v>57.5179</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0:57.52</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>56.0528</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.3103</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5067.3486</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:24:27.35</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:41;1:17;3:20;9:36;0:36;6:15;2:12;5:15;8:29;4:20</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[0,4,6,7];1:[4];3:[4,6];9:[4,7];0:[1,4,6];6:[4];2:[4];5:[];8:[1,4];4:[3]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=41,experts=[0,4,6,7]; c1:bw=17,experts=[4]; c3:bw=20,experts=[4,6]; c9:bw=36,experts=[4,7]; c0:bw=36,experts=[1,4,6]; c6:bw=15,experts=[4]; c2:bw=12,experts=[4]; c5:bw=15,experts=[]; c8:bw=29,experts=[1,4]; c4:bw=20,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>5.1145,4.7813,5.5676,3.8121,5.2300,7.3821,4.0702,6.8742,5.8257,7.3951</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:26:23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.449710410734614</v>
+      </c>
+      <c r="F92" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="G92" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H92" t="n">
+        <v>90</v>
+      </c>
+      <c r="I92" t="n">
+        <v>57.1458</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0:57.15</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>55.7494</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5124.5358</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:25:24.54</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:28;9:20;5:29;7:29;3:23;4:31;0:13;6:16;2:6;8:13</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[1];9:[1,4];5:[6];7:[3,4];3:[1,4];4:[4,5,7];0:[];6:[];2:[];8:[3]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[1]; c9:bw=20,experts=[1,4]; c5:bw=29,experts=[6]; c7:bw=29,experts=[3,4]; c3:bw=23,experts=[1,4]; c4:bw=31,experts=[4,5,7]; c0:bw=13,experts=[]; c6:bw=16,experts=[]; c2:bw=6,experts=[]; c8:bw=13,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>4.8646,3.8307,6.9568,4.9965,5.5002,7.3534,5.1681,7.1959,4.0334,5.8499</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:27:20</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.452419400857925</v>
+      </c>
+      <c r="F93" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="G93" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H93" t="n">
+        <v>90</v>
+      </c>
+      <c r="I93" t="n">
+        <v>57.2053</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0:57.21</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>55.7891</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.2792</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5181.7824</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:26:21.78</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:16;7:19;1:11;0:17;8:11;6:26;9:32;2:14;5:37;4:15</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[];7:[];1:[];0:[4];8:[4];6:[0,6];9:[0,4,6];2:[1];5:[2,3,7];4:[]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=16,experts=[]; c7:bw=19,experts=[]; c1:bw=11,experts=[]; c0:bw=17,experts=[4]; c8:bw=11,experts=[4]; c6:bw=26,experts=[0,6]; c9:bw=32,experts=[0,4,6]; c2:bw=14,experts=[1]; c5:bw=37,experts=[2,3,7]; c4:bw=15,experts=[]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>5.7159,5.0781,4.7383,5.2127,5.7909,7.1835,3.8966,4.1241,6.7565,7.2925</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:28:17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.466956156408388</v>
+      </c>
+      <c r="F94" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="G94" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H94" t="n">
+        <v>90</v>
+      </c>
+      <c r="I94" t="n">
+        <v>57.165</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0:57.17</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>55.8336</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5238.983</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:27:18.98</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:27;3:18;7:13;9:33;6:13;8:3;5:5;4:18;0:11;2:29</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[0,4];3:[0];7:[];9:[3,4,6];6:[1];8:[];5:[];4:[1];0:[];2:[0,2]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=27,experts=[0,4]; c3:bw=18,experts=[0]; c7:bw=13,experts=[]; c9:bw=33,experts=[3,4,6]; c6:bw=13,experts=[1]; c8:bw=3,experts=[]; c5:bw=5,experts=[]; c4:bw=18,experts=[1]; c0:bw=11,experts=[]; c2:bw=29,experts=[0,2]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>4.5149,5.2277,5.4470,3.9720,7.5637,6.2142,7.3393,7.0026,4.7984,3.7538</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:29:14</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.445328832736183</v>
+      </c>
+      <c r="F95" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="G95" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H95" t="n">
+        <v>90</v>
+      </c>
+      <c r="I95" t="n">
+        <v>56.7506</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0:56.75</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>55.3083</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5295.7692</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:28:15.77</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:25;2:37;5:23;4:18;6:17;9:28;1:40;8:4;0:31;3:19</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[1,4];2:[3,4,6];5:[4,5];4:[];6:[];9:[4];1:[0,2,4,6];8:[];0:[0,2,4];3:[3]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=25,experts=[1,4]; c2:bw=37,experts=[3,4,6]; c5:bw=23,experts=[4,5]; c4:bw=18,experts=[]; c6:bw=17,experts=[]; c9:bw=28,experts=[4]; c1:bw=40,experts=[0,2,4,6]; c8:bw=4,experts=[]; c0:bw=31,experts=[0,2,4]; c3:bw=19,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>4.6689,3.8552,6.9813,7.4007,7.2430,3.8086,4.7543,5.9169,5.1529,5.5264</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:30:11</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.440660743660636</v>
+      </c>
+      <c r="F96" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="G96" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H96" t="n">
+        <v>90</v>
+      </c>
+      <c r="I96" t="n">
+        <v>57.0841</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0:57.08</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>55.6805</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.2459</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5352.8885</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:29:12.89</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:34;9:24;4:9;6:23;0:20;3:23;1:18;8:43;2:13;5:5</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[0,4,6];9:[4,6];4:[];6:[2,3];0:[3,7];3:[2,5];1:[4];8:[2,4,7];2:[5];5:[]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=34,experts=[0,4,6]; c9:bw=24,experts=[4,6]; c4:bw=9,experts=[]; c6:bw=23,experts=[2,3]; c0:bw=20,experts=[3,7]; c3:bw=23,experts=[2,5]; c1:bw=18,experts=[4]; c8:bw=43,experts=[2,4,7]; c2:bw=13,experts=[5]; c5:bw=5,experts=[]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>5.1977,3.8427,7.5064,7.2229,5.1306,5.5187,4.6761,5.8480,4.0029,6.7345</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:31:08</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.430992303682362</v>
+      </c>
+      <c r="F97" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="G97" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
+      <c r="I97" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0:57.19</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>55.7734</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.2704</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5410.1227</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:30:10.12</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:37;9:25;3:26;1:20;5:34;4:28;6:18;7:29;0:20;8:36</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,4,6];9:[2,4];3:[4,7];1:[3,4];5:[0,4,6];4:[0,6];6:[5];7:[2,5];0:[4,5];8:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=37,experts=[0,4,6]; c9:bw=25,experts=[2,4]; c3:bw=26,experts=[4,7]; c1:bw=20,experts=[3,4]; c5:bw=34,experts=[0,4,6]; c4:bw=28,experts=[0,6]; c6:bw=18,experts=[5]; c7:bw=29,experts=[2,5]; c0:bw=20,experts=[4,5]; c8:bw=36,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>4.0997,3.8288,5.5380,4.8571,6.8051,7.3803,7.1952,4.9742,5.2729,5.8220</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:32:06</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.427933438719097</v>
+      </c>
+      <c r="F98" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="G98" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="H98" t="n">
+        <v>96</v>
+      </c>
+      <c r="I98" t="n">
+        <v>57.6447</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0:57.64</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>56.2043</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.3038</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5467.8114</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:31:07.81</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:23;9:24;8:24;4:9;7:17;1:28;3:20;5:26;6:28;2:31</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[4];9:[4,5];8:[4,5];4:[];7:[];1:[5];3:[4];5:[1,4];6:[7];2:[4,7]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=23,experts=[4]; c9:bw=24,experts=[4,5]; c8:bw=24,experts=[4,5]; c4:bw=9,experts=[]; c7:bw=17,experts=[]; c1:bw=28,experts=[5]; c3:bw=20,experts=[4]; c5:bw=26,experts=[1,4]; c6:bw=28,experts=[7]; c2:bw=31,experts=[4,7]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5.2125,3.8147,5.7880,7.4155,4.9944,4.7063,5.6268,6.9433,7.5590,4.1438</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:33:03</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.431785909384007</v>
+      </c>
+      <c r="F99" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="G99" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="H99" t="n">
+        <v>96</v>
+      </c>
+      <c r="I99" t="n">
+        <v>57.0394</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0:57.04</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>55.5949</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.2794</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5524.8873</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:32:04.89</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:29;8:30;9:15;7:13;6:21;5:28;0:19;3:14;1:15;2:14</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[2];8:[1,4,6];9:[7];7:[7];6:[4];5:[4,6];0:[1];3:[6];1:[7];2:[]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=29,experts=[2]; c8:bw=30,experts=[1,4,6]; c9:bw=15,experts=[7]; c7:bw=13,experts=[7]; c6:bw=21,experts=[4]; c5:bw=28,experts=[4,6]; c0:bw=19,experts=[1]; c3:bw=14,experts=[6]; c1:bw=15,experts=[7]; c2:bw=14,experts=[]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>7.4225,5.8200,3.8255,4.9876,7.2326,6.8196,5.2252,5.4483,4.7441,4.0694</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:34:00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.409592099221364</v>
+      </c>
+      <c r="F100" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="G100" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="H100" t="n">
+        <v>99</v>
+      </c>
+      <c r="I100" t="n">
+        <v>57.0662</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0:57.07</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>55.6546</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.2502</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5581.9998</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:33:02.00</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:19;5:28;7:26;1:34;3:21;9:12;4:14;0:23;2:17;6:20</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[3];5:[4];7:[3,4];1:[1,4,6];3:[1,4];9:[1];4:[];0:[4,6];2:[4];6:[4,6]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=19,experts=[3]; c5:bw=28,experts=[4]; c7:bw=26,experts=[3,4]; c1:bw=34,experts=[1,4,6]; c3:bw=21,experts=[1,4]; c9:bw=12,experts=[1]; c4:bw=14,experts=[]; c0:bw=23,experts=[4,6]; c2:bw=17,experts=[4]; c6:bw=20,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>5.8175,6.8223,5.0181,4.7368,5.6305,3.8149,7.3395,5.1803,3.9854,7.3092</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:34:57</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.406722990326664</v>
+      </c>
+      <c r="F101" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="G101" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="H101" t="n">
+        <v>99</v>
+      </c>
+      <c r="I101" t="n">
+        <v>56.805</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0:56.81</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>55.3533</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.2961</v>
+      </c>
+      <c r="N101" t="n">
+        <v>5638.8464</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:33:58.85</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:17;8:25;9:30;5:10;6:25;1:10;4:37;7:4;3:24;0:36</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[1];8:[4];9:[0,4];5:[];6:[0,4];1:[4];4:[3,4,5];7:[];3:[4,6];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=17,experts=[1]; c8:bw=25,experts=[4]; c9:bw=30,experts=[0,4]; c5:bw=10,experts=[]; c6:bw=25,experts=[0,4]; c1:bw=10,experts=[4]; c4:bw=37,experts=[3,4,5]; c7:bw=4,experts=[]; c3:bw=24,experts=[4,6]; c0:bw=36,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>4.1121,5.8491,3.8166,6.7614,7.2891,4.6751,7.2277,4.8674,5.5587,5.1961</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
